--- a/fixtures/excel-split-comma-values-into-rows_fixture.xlsx
+++ b/fixtures/excel-split-comma-values-into-rows_fixture.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>TEXTSPLIT(B2,",")</f>
+        <f>_xlfn.TEXTSPLIT(B2,",")</f>
         <v/>
       </c>
     </row>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C5">
-        <f>TEXTSPLIT(B5,",",,FALSE)</f>
+        <f>_xlfn.TEXTSPLIT(B5,",",,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="F6">
-        <f>TEXTSPLIT(B6,",",,TRUE)</f>
+        <f>_xlfn.TEXTSPLIT(B6,",",,TRUE)</f>
         <v/>
       </c>
     </row>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C9">
-        <f>TEXTSPLIT(B9,{",",";"})</f>
+        <f>_xlfn.TEXTSPLIT(B9,{",",";"})</f>
         <v/>
       </c>
     </row>
